--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
+        <v>יובל גולד – בית במושב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%95%d7%a6%d7%a8-%d7%a2%d7%a7%d7%99%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%97%d7%99%d7%9d-%d7%9c%d7%a8%d7%92%d7%a2/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%91%d7%99%d7%aa-%d7%91%d7%9e%d7%95%d7%a9%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "אורחים לרגע” של אליעזר בוצר ועקיבא תורג'מן הוא יצירה טעונה מאוד, שנעה בין שבר עמוק לבין מבט מפויס על החיים והנצח. יש בו תחושה כמעט נבואית כאילו הוא מביט על החיים מלמעלה, בפרספקטיבה של זמניות. המשפט החוזר “אנחנו רק</v>
+        <v>הטקסט של „"בית במושב” של יובל גולד עובד בדיוק על הקו שבין פשטות יומיומית לבין הצהרה רגשית עמוקה, בקצב שמשרת נרטיב אישי בבלדת רוק נוגה. השיר נשען על קצב יציב (כמעט “הליכה” רגועה), בלי שינויים דרמטיים: בינוני-איטי שיוצר תחושת אינטימיות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
+        <v>יובל גולד – בית במושב</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד – בית במושב</v>
+        <v>ויולט – בסוף יגיע הבוקר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%91%d7%99%d7%aa-%d7%91%d7%9e%d7%95%d7%a9%d7%91/</v>
+        <v>https://yosmusic.com/%d7%95%d7%99%d7%95%d7%9c%d7%98-%d7%91%d7%a1%d7%95%d7%a3-%d7%99%d7%92%d7%99%d7%a2-%d7%94%d7%91%d7%95%d7%a7%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הטקסט של „"בית במושב” של יובל גולד עובד בדיוק על הקו שבין פשטות יומיומית לבין הצהרה רגשית עמוקה, בקצב שמשרת נרטיב אישי בבלדת רוק נוגה. השיר נשען על קצב יציב (כמעט “הליכה” רגועה), בלי שינויים דרמטיים: בינוני-איטי שיוצר תחושת אינטימיות</v>
+        <v>"בסוף יגיע הבוקר” של ויולט לוקץ' הוא שיר של אופטימיות, כזו שמודעת לכך שלחושך יש נוכחות, רק לא נצח. המשפט: “בסוף יגיע הבוקר” לא רק מבטיח תקווה אלא מנסח תפיסת עולם: מצבים קשים הם זמניים, גם כשאין שליטה (“לא משנה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד – בית במושב</v>
+        <v>ויולט – בסוף יגיע הבוקר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ויולט – בסוף יגיע הבוקר</v>
+        <v>איציק איזמירלי – לא אמרת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%99%d7%95%d7%9c%d7%98-%d7%91%d7%a1%d7%95%d7%a3-%d7%99%d7%92%d7%99%d7%a2-%d7%94%d7%91%d7%95%d7%a7%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%a6%d7%99%d7%a7-%d7%90%d7%99%d7%96%d7%9e%d7%99%d7%a8%d7%9c%d7%99-%d7%9c%d7%90-%d7%90%d7%9e%d7%a8%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-26</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"בסוף יגיע הבוקר” של ויולט לוקץ' הוא שיר של אופטימיות, כזו שמודעת לכך שלחושך יש נוכחות, רק לא נצח. המשפט: “בסוף יגיע הבוקר” לא רק מבטיח תקווה אלא מנסח תפיסת עולם: מצבים קשים הם זמניים, גם כשאין שליטה (“לא משנה</v>
+        <v>איציק איזמירלי מקונן אהבה נכזבת בבלדה דרמטית שממקמת את עצמה עמוק בז’אנר של שירי שברון לב קלאסיים, בשפה ישירה מאוד וטון של זעקה לא מעובדת. כבר מהשורה – “מכל הנשים בעולם אהבתי רק אותך” נבנית תפיסה של אהבה בלעדית, טוטאלית,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ויולט – בסוף יגיע הבוקר</v>
+        <v>איציק איזמירלי – לא אמרת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איציק איזמירלי – לא אמרת</v>
+        <v>יערה טופ – רק את</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%a6%d7%99%d7%a7-%d7%90%d7%99%d7%96%d7%9e%d7%99%d7%a8%d7%9c%d7%99-%d7%9c%d7%90-%d7%90%d7%9e%d7%a8%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%98%d7%95%d7%a4-%d7%a8%d7%a7-%d7%90%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>איציק איזמירלי מקונן אהבה נכזבת בבלדה דרמטית שממקמת את עצמה עמוק בז’אנר של שירי שברון לב קלאסיים, בשפה ישירה מאוד וטון של זעקה לא מעובדת. כבר מהשורה – “מכל הנשים בעולם אהבתי רק אותך” נבנית תפיסה של אהבה בלעדית, טוטאלית,</v>
+        <v>השיר "רק את” של יערה טופ הוא טקסט טעון שמצליח ללכוד רגע מאוד ספציפי אחרי פרידה: הרגע שבו הצד שעזב חוזר לא מאהבה מחודשת, אלא מתוך חולשה, בדידות או חרטה. הדוברת מציבה גבול ברור, ובכך הופכת את השיר לא רק</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איציק איזמירלי – לא אמרת</v>
+        <v>יערה טופ – רק את</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יערה טופ – רק את</v>
+        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%98%d7%95%d7%a4-%d7%a8%d7%a7-%d7%90%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9e%d7%94-%d7%90%d7%9d-%d7%94%d7%99%d7%99%d7%aa%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "רק את” של יערה טופ הוא טקסט טעון שמצליח ללכוד רגע מאוד ספציפי אחרי פרידה: הרגע שבו הצד שעזב חוזר לא מאהבה מחודשת, אלא מתוך חולשה, בדידות או חרטה. הדוברת מציבה גבול ברור, ובכך הופכת את השיר לא רק</v>
+        <v>"מה אם הייתי” בביצוע הדואט של מוש בן ארי ואברהם טל מציג גישה שונה מאוד לשאלת העבר והחרטה: במקום התחשבנות כואבת, יש כאן השלמה, קלילות ואפילו חגיגה של מה שהיה. על פניו, השיר בנוי סביב שאלה קלאסית – "מה אם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יערה טופ – רק את</v>
+        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
+        <v>כברה קסאי – שמש באה בזמן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9e%d7%94-%d7%90%d7%9d-%d7%94%d7%99%d7%99%d7%aa%d7%99/</v>
+        <v>https://yosmusic.com/%d7%9b%d7%91%d7%a8%d7%94-%d7%a7%d7%a1%d7%90%d7%99-%d7%a9%d7%9e%d7%a9-%d7%91%d7%90%d7%94-%d7%91%d7%96%d7%9e%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"מה אם הייתי” בביצוע הדואט של מוש בן ארי ואברהם טל מציג גישה שונה מאוד לשאלת העבר והחרטה: במקום התחשבנות כואבת, יש כאן השלמה, קלילות ואפילו חגיגה של מה שהיה. על פניו, השיר בנוי סביב שאלה קלאסית – "מה אם</v>
+        <v>השיר "ושמש באה בזמן” של כברה קסאי הוא שיר אינטימי ועדין שמצליח להישמע כמו תפילה אישית, ובו בזמן לגעת בפחד אוניברסלי: דאגה לאדם קרוב שנמצא רחוק, בסכנה. לב השיר נמצא במתח בין שני כוחות: חרדה וחוסר שליטה ("בלילות קשה…”, „קולות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
+        <v>כברה קסאי – שמש באה בזמן</v>
       </c>
     </row>
   </sheetData>
